--- a/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:51:40+00:00</t>
+    <t>2025-05-06T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T13:54:59+00:00</t>
+    <t>2025-05-14T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="132">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:00:47+00:00</t>
+    <t>2025-05-22T16:12:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Extension transportant les statuts spécifiques de la pré-admission.</t>
+    <t>Statut de pré-admission</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -344,36 +344,17 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.fr/fhir/fr/preadmission/ValueSet/preadmission-statuts-vs</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>Extension.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>PreAdmissionStatusValueSet</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
     <t>Extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valueCodeableConcept.extension</t>
   </si>
   <si>
     <t>Extension.value[x].extension</t>
@@ -392,9 +373,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Extension.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
     <t>Extension.value[x].coding</t>
   </si>
   <si>
@@ -421,140 +399,6 @@
   </si>
   <si>
     <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valueCodeableConcept.coding.id</t>
-  </si>
-  <si>
-    <t>Extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valueCodeableConcept.coding.extension</t>
-  </si>
-  <si>
-    <t>Extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valueCodeableConcept.coding.system</t>
-  </si>
-  <si>
-    <t>Extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valueCodeableConcept.coding.version</t>
-  </si>
-  <si>
-    <t>Extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valueCodeableConcept.coding.code</t>
-  </si>
-  <si>
-    <t>Extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valueCodeableConcept.coding.display</t>
-  </si>
-  <si>
-    <t>Extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valueCodeableConcept.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valueCodeableConcept.text</t>
   </si>
   <si>
     <t>Extension.value[x].text</t>
@@ -893,12 +737,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK18"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.0546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="23.75" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="23.75" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -921,7 +765,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="23.55859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.8125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -1522,26 +1366,26 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AC6" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>103</v>
@@ -1567,17 +1411,15 @@
         <v>110</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>84</v>
@@ -1592,13 +1434,13 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1625,11 +1467,13 @@
         <v>77</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y7" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y7" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z7" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>77</v>
@@ -1647,7 +1491,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1659,29 +1503,29 @@
         <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>77</v>
@@ -1693,15 +1537,17 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N8" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>77</v>
@@ -1738,31 +1584,31 @@
         <v>77</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>89</v>
@@ -1773,15 +1619,15 @@
         <v>116</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -1793,10 +1639,10 @@
         <v>77</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="L9" t="s" s="2">
         <v>119</v>
@@ -1807,7 +1653,9 @@
       <c r="N9" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="O9" s="2"/>
+      <c r="O9" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="P9" t="s" s="2">
         <v>77</v>
       </c>
@@ -1843,19 +1691,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -1867,18 +1715,18 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>89</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1886,7 +1734,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>84</v>
@@ -1898,10 +1746,10 @@
         <v>77</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>126</v>
@@ -1968,7 +1816,7 @@
         <v>78</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>77</v>
@@ -1978,850 +1826,6 @@
       </c>
       <c r="AK10" t="s" s="2">
         <v>131</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K11" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK11" t="s" s="2">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O12" s="2"/>
-      <c r="P12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="K13" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="P13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="K14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="P15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="P16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="P17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q17" s="2"/>
-      <c r="R17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="K18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="P18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q18" s="2"/>
-      <c r="R18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T15:02:23+00:00</t>
+    <t>2025-10-22T09:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-22T09:09:51+00:00</t>
+    <t>2025-10-28T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T12:51:21+00:00</t>
+    <t>2026-02-24T09:27:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
+++ b/nmoreau/ig/StructureDefinition-statut-preadmission-fr.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T09:27:09+00:00</t>
+    <t>2026-04-10T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
